--- a/excel/8_Text_Functions.xlsx
+++ b/excel/8_Text_Functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\asilbek\data_analysis\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482EDF11-EDAF-4CC2-A932-C9ECA68ABB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72192CD-3601-4F72-8800-AE9DF70A0AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" r:id="rId1"/>
@@ -1842,12 +1842,12 @@
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="9" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="22" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="40" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="8.85546875" customWidth="1"/>
     <col min="10" max="10" width="34.7109375" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" customWidth="1"/>
@@ -1935,6 +1935,10 @@
         <f>_xlfn.TEXTJOIN(" ", TRUE, F2, G2)</f>
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
+      <c r="L2" t="str">
+        <f>LEFT(B2, 5)</f>
+        <v>Pam B</v>
+      </c>
       <c r="Q2">
         <f>FIND(",", G2)+LEN(", ")</f>
         <v>11</v>
@@ -1974,23 +1978,23 @@
         <v>14</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J22" si="0">_xlfn.TEXTJOIN(" ", TRUE, F3, G3)</f>
+        <f t="shared" ref="J3:J21" si="0">_xlfn.TEXTJOIN(" ", TRUE, F3, G3)</f>
         <v>203 Birch St Chicago, IL, 60601</v>
       </c>
-      <c r="L3" t="e">
-        <f>LEFT(B2,3)+_xlfn.ARRAYTOTEXT(B2)+_xlfn.VALUETOTEXT(B2)</f>
-        <v>#VALUE!</v>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L21" si="1">LEFT(B3, 5)</f>
+        <v>Micha</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q21" si="1">FIND(",", G3)+LEN(", ")</f>
+        <f t="shared" ref="Q3:Q21" si="2">FIND(",", G3)+LEN(", ")</f>
         <v>10</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R21" si="2">FIND(",",G3,Q3)</f>
+        <f t="shared" ref="R3:R21" si="3">FIND(",",G3,Q3)</f>
         <v>12</v>
       </c>
       <c r="S3" t="str">
-        <f t="shared" ref="S3:S21" si="3">MID(G3,Q3,R3-Q3)</f>
+        <f t="shared" ref="S3:S21" si="4">MID(G3,Q3,R3-Q3)</f>
         <v>IL</v>
       </c>
     </row>
@@ -2024,19 +2028,19 @@
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
       <c r="L4" t="str">
-        <f t="shared" ref="L4:L21" si="4">LEFT(B3,3)</f>
-        <v>Mic</v>
+        <f t="shared" si="1"/>
+        <v>Kevin</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
     </row>
@@ -2070,19 +2074,19 @@
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
       <c r="L5" t="str">
+        <f t="shared" si="1"/>
+        <v>Pam B</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="S5" t="str">
         <f t="shared" si="4"/>
-        <v>Kev</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="S5" t="str">
-        <f t="shared" si="3"/>
         <v>CA</v>
       </c>
     </row>
@@ -2116,19 +2120,19 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
       <c r="L6" t="str">
+        <f t="shared" si="1"/>
+        <v>Jim H</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="S6" t="str">
         <f t="shared" si="4"/>
-        <v>Pam</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="S6" t="str">
-        <f t="shared" si="3"/>
         <v>PA</v>
       </c>
     </row>
@@ -2162,19 +2166,19 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
       <c r="L7" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Ryan </v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="S7" t="str">
         <f t="shared" si="4"/>
-        <v>Jim</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="S7" t="str">
-        <f t="shared" si="3"/>
         <v>PA</v>
       </c>
     </row>
@@ -2208,19 +2212,19 @@
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
       <c r="L8" t="str">
+        <f t="shared" si="1"/>
+        <v>Kevin</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="S8" t="str">
         <f t="shared" si="4"/>
-        <v>Rya</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="S8" t="str">
-        <f t="shared" si="3"/>
         <v>IL</v>
       </c>
     </row>
@@ -2254,19 +2258,19 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
       <c r="L9" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Ryan </v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="S9" t="str">
         <f t="shared" si="4"/>
-        <v>Kev</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="S9" t="str">
-        <f t="shared" si="3"/>
         <v>PA</v>
       </c>
     </row>
@@ -2300,19 +2304,19 @@
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
       <c r="L10" t="str">
+        <f t="shared" si="1"/>
+        <v>Stanl</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="S10" t="str">
         <f t="shared" si="4"/>
-        <v>Rya</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="S10" t="str">
-        <f t="shared" si="3"/>
         <v>IL</v>
       </c>
     </row>
@@ -2346,19 +2350,19 @@
         <v>123 Elm St Los Angeles, CA, 90001</v>
       </c>
       <c r="L11" t="str">
+        <f t="shared" si="1"/>
+        <v>Angel</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="S11" t="str">
         <f t="shared" si="4"/>
-        <v>Sta</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="S11" t="str">
-        <f t="shared" si="3"/>
         <v>CA</v>
       </c>
     </row>
@@ -2392,19 +2396,19 @@
         <v>123 Elm St San Diego, CA, 92101</v>
       </c>
       <c r="L12" t="str">
+        <f t="shared" si="1"/>
+        <v>Dwigh</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="S12" t="str">
         <f t="shared" si="4"/>
-        <v>Ang</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="S12" t="str">
-        <f t="shared" si="3"/>
         <v>CA</v>
       </c>
     </row>
@@ -2438,19 +2442,19 @@
         <v>202 Birch St Chicago, IL, 60601</v>
       </c>
       <c r="L13" t="str">
+        <f t="shared" si="1"/>
+        <v>Oscar</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="S13" t="str">
         <f t="shared" si="4"/>
-        <v>Dwi</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="S13" t="str">
-        <f t="shared" si="3"/>
         <v>IL</v>
       </c>
     </row>
@@ -2484,19 +2488,19 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
       <c r="L14" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Ryan </v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="S14" t="str">
         <f t="shared" si="4"/>
-        <v>Osc</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="S14" t="str">
-        <f t="shared" si="3"/>
         <v>PA</v>
       </c>
     </row>
@@ -2530,19 +2534,19 @@
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
       <c r="L15" t="str">
+        <f t="shared" si="1"/>
+        <v>Phyll</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="S15" t="str">
         <f t="shared" si="4"/>
-        <v>Rya</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="S15" t="str">
-        <f t="shared" si="3"/>
         <v>IL</v>
       </c>
     </row>
@@ -2576,19 +2580,19 @@
         <v>456 Oak St Chicago, IL, 60601</v>
       </c>
       <c r="L16" t="str">
+        <f t="shared" si="1"/>
+        <v>Mered</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="S16" t="str">
         <f t="shared" si="4"/>
-        <v>Phy</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="S16" t="str">
-        <f t="shared" si="3"/>
         <v>IL</v>
       </c>
     </row>
@@ -2622,19 +2626,19 @@
         <v>203 Birch St Chicago, IL, 60602</v>
       </c>
       <c r="L17" t="str">
+        <f t="shared" si="1"/>
+        <v>Micha</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="S17" t="str">
         <f t="shared" si="4"/>
-        <v>Mer</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="S17" t="str">
-        <f t="shared" si="3"/>
         <v>IL</v>
       </c>
     </row>
@@ -2668,19 +2672,19 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
       <c r="L18" t="str">
+        <f t="shared" si="1"/>
+        <v>Jim H</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="S18" t="str">
         <f t="shared" si="4"/>
-        <v>Mic</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="S18" t="str">
-        <f t="shared" si="3"/>
         <v>PA</v>
       </c>
     </row>
@@ -2714,19 +2718,19 @@
         <v>456 Oak St New York, NY, 10001</v>
       </c>
       <c r="L19" t="str">
+        <f t="shared" si="1"/>
+        <v>Kelly</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="S19" t="str">
         <f t="shared" si="4"/>
-        <v>Jim</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="S19" t="str">
-        <f t="shared" si="3"/>
         <v>NY</v>
       </c>
     </row>
@@ -2760,19 +2764,19 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
       <c r="L20" t="str">
+        <f t="shared" si="1"/>
+        <v>Jim H</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="S20" t="str">
         <f t="shared" si="4"/>
-        <v>Kel</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="S20" t="str">
-        <f t="shared" si="3"/>
         <v>PA</v>
       </c>
     </row>
@@ -2806,25 +2810,25 @@
         <v>459 Oak St New York, NY, 10001</v>
       </c>
       <c r="L21" t="str">
+        <f t="shared" si="1"/>
+        <v>Jim H</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="S21" t="str">
         <f t="shared" si="4"/>
-        <v>Jim</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="S21" t="str">
-        <f t="shared" si="3"/>
         <v>NY</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J3:J22" si="5">_xlfn.TEXTJOIN(" ", TRUE, F22, G22)</f>
         <v/>
       </c>
     </row>
